--- a/FLORES DE ESTRADA/Mayo/PRORRATEO MAYO Estrada.xlsx
+++ b/FLORES DE ESTRADA/Mayo/PRORRATEO MAYO Estrada.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BE5C5A-62B0-4413-A417-8A08A6A419BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B006D3EE-9EC7-48B2-A003-A007BB84086E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="83">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -253,9 +253,6 @@
     <t>Daniel</t>
   </si>
   <si>
-    <t>David</t>
-  </si>
-  <si>
     <t>Raquel</t>
   </si>
   <si>
@@ -274,7 +271,10 @@
     <t xml:space="preserve">Antonella </t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 14/05  LIQUIDACION : ABRIL</t>
+    <t>EXPENSAS - VENCIMIENTO 10/06 LIQUIDACION : MAYO</t>
+  </si>
+  <si>
+    <t>Federico</t>
   </si>
 </sst>
 </file>
@@ -721,8 +721,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="15" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -744,6 +742,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1097,28 +1097,28 @@
     <col min="9" max="9" width="8.42578125" style="6" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" customWidth="1"/>
     <col min="11" max="11" width="11.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
     <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="69"/>
+      <c r="A1" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="67"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
@@ -1151,13 +1151,13 @@
       <c r="I4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="65">
+      <c r="J4" s="63">
         <v>1153202676</v>
       </c>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="66"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="64"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
@@ -1188,7 +1188,7 @@
         <v>56</v>
       </c>
       <c r="C7" s="50">
-        <v>1308068.92</v>
+        <v>1245701.98</v>
       </c>
       <c r="D7" s="53"/>
       <c r="F7" s="7"/>
@@ -1283,11 +1283,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F11" s="5">
-        <v>45954.773480000003</v>
-      </c>
-      <c r="G11" s="62">
+        <v>64095.377079999998</v>
+      </c>
+      <c r="G11" s="69">
         <f>F11</f>
-        <v>45954.773480000003</v>
+        <v>64095.377079999998</v>
       </c>
       <c r="H11" s="8">
         <f>F11-G11</f>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="L11" s="5">
         <f>C7*E11/100</f>
-        <v>64095.377079999998</v>
+        <v>61039.397020000004</v>
       </c>
       <c r="M11" s="5">
         <f>C8*E11/100</f>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="N11" s="44">
         <f>K11+L11+M11</f>
-        <v>64095.377079999998</v>
+        <v>61039.397020000004</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1332,27 +1332,27 @@
         <v>3.89</v>
       </c>
       <c r="F12" s="5">
-        <v>342358.67195682006</v>
-      </c>
-      <c r="G12" s="62"/>
+        <v>423370.11607702024</v>
+      </c>
+      <c r="G12" s="69"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
-        <v>342358.67195682006</v>
+        <v>423370.11607702024</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" ref="J12:J34" si="1">H12*8.8%</f>
-        <v>30127.563132200168</v>
+        <v>37256.570214777785</v>
       </c>
       <c r="K12" s="44">
         <f>H12+I12+J12</f>
-        <v>372486.23508902022</v>
+        <v>460626.68629179802</v>
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
-        <v>50883.880987999997</v>
+        <v>48457.807022000001</v>
       </c>
       <c r="M12" s="5">
         <f>C8*E12/100</f>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>423370.11607702024</v>
+        <v>509084.49331379804</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1374,35 +1374,36 @@
         <v>7</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" s="3">
         <v>4</v>
       </c>
       <c r="F13" s="5">
-        <v>43134.480339672315</v>
-      </c>
-      <c r="G13" s="62">
-        <v>37514</v>
+        <v>58437.839409563472</v>
+      </c>
+      <c r="G13" s="69">
+        <f>F13</f>
+        <v>58437.839409563472</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="0"/>
-        <v>5620.4803396723146</v>
+        <v>0</v>
       </c>
       <c r="I13" s="5">
         <v>0</v>
       </c>
       <c r="J13" s="9">
         <f t="shared" si="1"/>
-        <v>494.60226989116376</v>
+        <v>0</v>
       </c>
       <c r="K13" s="44">
         <f>H13+I13+J13</f>
-        <v>6115.0826095634784</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
         <f>C7*E13/100</f>
-        <v>52322.756799999996</v>
+        <v>49828.0792</v>
       </c>
       <c r="M13" s="5">
         <f>C8*E13/100</f>
@@ -1410,7 +1411,7 @@
       </c>
       <c r="N13" s="44">
         <f>K13+L13+M13</f>
-        <v>58437.839409563472</v>
+        <v>49828.0792</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1430,11 +1431,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F14" s="5">
-        <v>45954.773480000003</v>
-      </c>
-      <c r="G14" s="62">
+        <v>64095.377079999998</v>
+      </c>
+      <c r="G14" s="69">
         <f t="shared" ref="G14" si="2">F14</f>
-        <v>45954.773480000003</v>
+        <v>64095.377079999998</v>
       </c>
       <c r="H14" s="8">
         <f t="shared" si="0"/>
@@ -1453,7 +1454,7 @@
       </c>
       <c r="L14" s="5">
         <f>C7*E14/100</f>
-        <v>64095.377079999998</v>
+        <v>61039.397020000004</v>
       </c>
       <c r="M14" s="5">
         <f>C8*E14/100</f>
@@ -1461,7 +1462,7 @@
       </c>
       <c r="N14" s="44">
         <f t="shared" ref="N14:N24" si="3">K14+L14+M14</f>
-        <v>64095.377079999998</v>
+        <v>61039.397020000004</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1481,11 +1482,11 @@
         <v>3.89</v>
       </c>
       <c r="F15" s="5">
-        <v>36482.463027999998</v>
-      </c>
-      <c r="G15" s="62">
-        <f t="shared" ref="G15:G22" si="4">F15</f>
-        <v>36482.463027999998</v>
+        <v>50883.880987999997</v>
+      </c>
+      <c r="G15" s="69">
+        <f t="shared" ref="G15:G21" si="4">F15</f>
+        <v>50883.880987999997</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="0"/>
@@ -1504,7 +1505,7 @@
       </c>
       <c r="L15" s="5">
         <f>C7*E15/100</f>
-        <v>50883.880987999997</v>
+        <v>48457.807022000001</v>
       </c>
       <c r="M15" s="5">
         <f>C8*E15/100</f>
@@ -1512,7 +1513,7 @@
       </c>
       <c r="N15" s="44">
         <f>K15+L15+M15</f>
-        <v>50883.880987999997</v>
+        <v>48457.807022000001</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -1526,36 +1527,33 @@
         <v>9</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16" s="3">
         <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>37514.1008</v>
-      </c>
-      <c r="G16" s="62">
-        <f t="shared" si="4"/>
-        <v>37514.1008</v>
-      </c>
+        <v>52322.756799999996</v>
+      </c>
+      <c r="G16" s="69"/>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>52322.756799999996</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4604.4025984</v>
       </c>
       <c r="K16" s="44">
         <f>H16+J16+I16</f>
-        <v>0</v>
+        <v>56927.159398399992</v>
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
-        <v>52322.756799999996</v>
+        <v>49828.0792</v>
       </c>
       <c r="M16" s="5">
         <f>C8*E16/100</f>
@@ -1563,7 +1561,7 @@
       </c>
       <c r="N16" s="44">
         <f t="shared" si="3"/>
-        <v>52322.756799999996</v>
+        <v>106755.2385984</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1583,11 +1581,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F17" s="5">
-        <v>45954.773480000003</v>
-      </c>
-      <c r="G17" s="62">
+        <v>64095.377079999998</v>
+      </c>
+      <c r="G17" s="69">
         <f t="shared" si="4"/>
-        <v>45954.773480000003</v>
+        <v>64095.377079999998</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="0"/>
@@ -1606,7 +1604,7 @@
       </c>
       <c r="L17" s="5">
         <f>C7*E17/100</f>
-        <v>64095.377079999998</v>
+        <v>61039.397020000004</v>
       </c>
       <c r="M17" s="5">
         <f>C8*E17/100</f>
@@ -1614,7 +1612,7 @@
       </c>
       <c r="N17" s="44">
         <f>K17+L17+M17</f>
-        <v>64095.377079999998</v>
+        <v>61039.397020000004</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -1632,11 +1630,11 @@
         <v>3.89</v>
       </c>
       <c r="F18" s="5">
-        <v>36482.463027999998</v>
-      </c>
-      <c r="G18" s="62">
+        <v>50883.880987999997</v>
+      </c>
+      <c r="G18" s="69">
         <f t="shared" si="4"/>
-        <v>36482.463027999998</v>
+        <v>50883.880987999997</v>
       </c>
       <c r="H18" s="8">
         <f t="shared" si="0"/>
@@ -1655,7 +1653,7 @@
       </c>
       <c r="L18" s="5">
         <f>C7*E18/100</f>
-        <v>50883.880987999997</v>
+        <v>48457.807022000001</v>
       </c>
       <c r="M18" s="5">
         <f>C8*E18/100</f>
@@ -1663,7 +1661,7 @@
       </c>
       <c r="N18" s="44">
         <f t="shared" si="3"/>
-        <v>50883.880987999997</v>
+        <v>48457.807022000001</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -1677,17 +1675,17 @@
         <v>21</v>
       </c>
       <c r="D19" s="55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E19" s="3">
         <v>4</v>
       </c>
       <c r="F19" s="5">
-        <v>37514.1008</v>
-      </c>
-      <c r="G19" s="62">
+        <v>52322.756799999996</v>
+      </c>
+      <c r="G19" s="69">
         <f>F19</f>
-        <v>37514.1008</v>
+        <v>52322.756799999996</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="0"/>
@@ -1706,7 +1704,7 @@
       </c>
       <c r="L19" s="5">
         <f>C7*E19/100</f>
-        <v>52322.756799999996</v>
+        <v>49828.0792</v>
       </c>
       <c r="M19" s="5">
         <f>C8*E19/100</f>
@@ -1714,7 +1712,7 @@
       </c>
       <c r="N19" s="44">
         <f t="shared" si="3"/>
-        <v>52322.756799999996</v>
+        <v>49828.0792</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -1725,18 +1723,18 @@
         <v>22</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20" s="55"/>
       <c r="E20" s="1">
         <v>12.66</v>
       </c>
       <c r="F20" s="5">
-        <v>118732.12903200001</v>
-      </c>
-      <c r="G20" s="62">
+        <v>165601.525272</v>
+      </c>
+      <c r="G20" s="69">
         <f t="shared" si="4"/>
-        <v>118732.12903200001</v>
+        <v>165601.525272</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="0"/>
@@ -1755,7 +1753,7 @@
       </c>
       <c r="L20" s="5">
         <f>C7*E20/100</f>
-        <v>165601.525272</v>
+        <v>157705.87066799999</v>
       </c>
       <c r="M20" s="5">
         <f>C8*E20/100</f>
@@ -1763,7 +1761,7 @@
       </c>
       <c r="N20" s="44">
         <f>K20+L20+M20</f>
-        <v>165601.525272</v>
+        <v>157705.87066799999</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -1783,11 +1781,11 @@
         <v>7.75</v>
       </c>
       <c r="F21" s="5">
-        <v>72683.570300000007</v>
-      </c>
-      <c r="G21" s="63">
+        <v>101375.34129999999</v>
+      </c>
+      <c r="G21" s="70">
         <f t="shared" si="4"/>
-        <v>72683.570300000007</v>
+        <v>101375.34129999999</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="0"/>
@@ -1806,7 +1804,7 @@
       </c>
       <c r="L21" s="5">
         <f>C7*E21/100</f>
-        <v>101375.34129999999</v>
+        <v>96541.903450000013</v>
       </c>
       <c r="M21" s="5">
         <f>C8*E21/100</f>
@@ -1814,7 +1812,7 @@
       </c>
       <c r="N21" s="44">
         <f t="shared" si="3"/>
-        <v>101375.34129999999</v>
+        <v>96541.903450000013</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -1825,36 +1823,39 @@
         <v>24</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D22" s="55" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E22" s="1">
         <v>7.51</v>
       </c>
       <c r="F22" s="5">
-        <v>70432.724252</v>
-      </c>
-      <c r="G22" s="62"/>
+        <v>174866.77987817599</v>
+      </c>
+      <c r="G22" s="69">
+        <f>F22</f>
+        <v>174866.77987817599</v>
+      </c>
       <c r="H22" s="8">
         <f t="shared" si="0"/>
-        <v>70432.724252</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>6198.0797341760008</v>
+        <v>0</v>
       </c>
       <c r="K22" s="44">
         <f t="shared" ref="K22:K24" si="6">H22+J22+I22</f>
-        <v>76630.803986176004</v>
+        <v>0</v>
       </c>
       <c r="L22" s="5">
         <f>C7*E22/100</f>
-        <v>98235.975891999988</v>
+        <v>93552.218697999997</v>
       </c>
       <c r="M22" s="5">
         <f>C8*E22/100</f>
@@ -1862,7 +1863,7 @@
       </c>
       <c r="N22" s="44">
         <f t="shared" si="3"/>
-        <v>174866.77987817599</v>
+        <v>93552.218697999997</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1880,27 +1881,27 @@
         <v>4.45</v>
       </c>
       <c r="F23" s="5">
-        <v>41734.437140000002</v>
-      </c>
-      <c r="G23" s="62"/>
+        <v>103616.13454832</v>
+      </c>
+      <c r="G23" s="69"/>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>41734.437140000002</v>
+        <v>103616.13454832</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>3672.6304683200005</v>
+        <v>9118.2198402521608</v>
       </c>
       <c r="K23" s="44">
         <f>H23+J23+I23</f>
-        <v>45407.067608320001</v>
+        <v>112734.35438857216</v>
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
-        <v>58209.066940000004</v>
+        <v>55433.738109999998</v>
       </c>
       <c r="M23" s="5">
         <f>C8*E23/100</f>
@@ -1908,7 +1909,7 @@
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>103616.13454832</v>
+        <v>168168.09249857216</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1926,11 +1927,11 @@
         <v>6.17</v>
       </c>
       <c r="F24" s="5">
-        <v>57865.500483999997</v>
-      </c>
-      <c r="G24" s="62">
+        <v>80707.852363999991</v>
+      </c>
+      <c r="G24" s="69">
         <f>F24</f>
-        <v>57865.500483999997</v>
+        <v>80707.852363999991</v>
       </c>
       <c r="H24" s="8">
         <f t="shared" si="0"/>
@@ -1949,7 +1950,7 @@
       </c>
       <c r="L24" s="5">
         <f>C7*E24/100</f>
-        <v>80707.852363999991</v>
+        <v>76859.812166000003</v>
       </c>
       <c r="M24" s="5">
         <f>C8*E24/100</f>
@@ -1957,7 +1958,7 @@
       </c>
       <c r="N24" s="44">
         <f t="shared" si="3"/>
-        <v>80707.852363999991</v>
+        <v>76859.812166000003</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -1971,36 +1972,33 @@
         <v>5</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E25" s="1">
         <v>4.45</v>
       </c>
       <c r="F25" s="5">
-        <v>172796.45901858734</v>
-      </c>
-      <c r="G25" s="62">
-        <f>41735*2</f>
-        <v>83470</v>
-      </c>
+        <v>155397.25435222301</v>
+      </c>
+      <c r="G25" s="69"/>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>89326.459018587339</v>
+        <v>155397.25435222301</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>7860.7283936356862</v>
+        <v>13674.958382995626</v>
       </c>
       <c r="K25" s="44">
         <f>H25+J25+I25</f>
-        <v>97187.187412223022</v>
+        <v>169072.21273521864</v>
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
-        <v>58210.066940000004</v>
+        <v>55434.738109999998</v>
       </c>
       <c r="M25" s="5">
         <f>C8*E25/100</f>
@@ -2008,7 +2006,7 @@
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>155397.25435222301</v>
+        <v>224506.95084521864</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2028,29 +2026,27 @@
         <v>9.19</v>
       </c>
       <c r="F26" s="5">
-        <v>423273.41998854274</v>
-      </c>
-      <c r="G26" s="62">
-        <v>86190</v>
-      </c>
+        <v>486959.29469553451</v>
+      </c>
+      <c r="G26" s="69"/>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>337083.41998854274</v>
+        <v>486959.29469553451</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>29663.340958991765</v>
+        <v>42852.417933207042</v>
       </c>
       <c r="K26" s="44">
         <f>H26+J26+I26</f>
-        <v>366746.76094753452</v>
+        <v>529811.71262874152</v>
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
-        <v>120212.53374799999</v>
+        <v>114481.011962</v>
       </c>
       <c r="M26" s="5">
         <f>C8*E26/100</f>
@@ -2058,7 +2054,7 @@
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>486959.29469553451</v>
+        <v>644292.72459074156</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2078,11 +2074,11 @@
         <v>1.18</v>
       </c>
       <c r="F27" s="5">
-        <v>11067.659736</v>
-      </c>
-      <c r="G27" s="62">
+        <v>15436.213255999999</v>
+      </c>
+      <c r="G27" s="69">
         <f>F27</f>
-        <v>11067.659736</v>
+        <v>15436.213255999999</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="0"/>
@@ -2101,7 +2097,7 @@
       </c>
       <c r="L27" s="5">
         <f>C7*E27/100+1</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
       <c r="M27" s="5">
         <f>C8*E27/100</f>
@@ -2109,7 +2105,7 @@
       </c>
       <c r="N27" s="44">
         <f>K27+L27+M27</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2127,30 +2123,27 @@
         <v>1.18</v>
       </c>
       <c r="F28" s="5">
-        <v>11067.659736</v>
-      </c>
-      <c r="G28" s="62">
-        <f>F28</f>
-        <v>11067.659736</v>
-      </c>
+        <v>15436.213255999999</v>
+      </c>
+      <c r="G28" s="69"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15436.213255999999</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1358.386766528</v>
       </c>
       <c r="K28" s="44">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>16794.600022528</v>
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
       <c r="M28" s="5">
         <f>C8*E28/100</f>
@@ -2158,7 +2151,7 @@
       </c>
       <c r="N28" s="44">
         <f t="shared" ref="N28:N34" si="8">K28+L28+M28</f>
-        <v>15436.213255999999</v>
+        <v>31494.883386527999</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2176,30 +2169,27 @@
         <v>1.18</v>
       </c>
       <c r="F29" s="5">
-        <v>11067.659736</v>
-      </c>
-      <c r="G29" s="62">
-        <f t="shared" ref="G29:G33" si="9">F29</f>
-        <v>11067.659736</v>
-      </c>
+        <v>15436.213255999999</v>
+      </c>
+      <c r="G29" s="69"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15436.213255999999</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1358.386766528</v>
       </c>
       <c r="K29" s="44">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>16794.600022528</v>
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
       <c r="M29" s="5">
         <f>C8*E29/100</f>
@@ -2207,7 +2197,7 @@
       </c>
       <c r="N29" s="44">
         <f t="shared" si="8"/>
-        <v>15436.213255999999</v>
+        <v>31494.883386527999</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2225,29 +2215,29 @@
         <v>1.18</v>
       </c>
       <c r="F30" s="5">
-        <v>53931.310041132871</v>
-      </c>
-      <c r="G30" s="62">
+        <v>62071.494580752566</v>
+      </c>
+      <c r="G30" s="69">
         <v>11068</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
-        <v>42863.310041132871</v>
+        <v>51003.494580752566</v>
       </c>
       <c r="I30" s="5">
         <v>0</v>
       </c>
       <c r="J30" s="9">
         <f t="shared" si="1"/>
-        <v>3771.9712836196932</v>
+        <v>4488.3075231062267</v>
       </c>
       <c r="K30" s="44">
         <f t="shared" si="7"/>
-        <v>46635.281324752563</v>
+        <v>55491.80210385879</v>
       </c>
       <c r="L30" s="5">
         <f>C7*E30/100+1</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
       <c r="M30" s="5">
         <f>C8*E30/100</f>
@@ -2255,7 +2245,7 @@
       </c>
       <c r="N30" s="44">
         <f>K30+L30+M30</f>
-        <v>62071.494580752566</v>
+        <v>70192.085467858793</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2266,18 +2256,18 @@
         <v>38</v>
       </c>
       <c r="C31" s="55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D31" s="55"/>
       <c r="E31" s="1">
         <v>1.18</v>
       </c>
       <c r="F31" s="5">
-        <v>11067.659736</v>
-      </c>
-      <c r="G31" s="62">
-        <f t="shared" si="9"/>
-        <v>11067.659736</v>
+        <v>15436.213255999999</v>
+      </c>
+      <c r="G31" s="69">
+        <f t="shared" ref="G29:G33" si="9">F31</f>
+        <v>15436.213255999999</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="0"/>
@@ -2296,7 +2286,7 @@
       </c>
       <c r="L31" s="5">
         <f>C7*E31/100+1</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
       <c r="M31" s="5">
         <f>C8*E31/100</f>
@@ -2304,7 +2294,7 @@
       </c>
       <c r="N31" s="44">
         <f>K31+L31+M31</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -2322,11 +2312,11 @@
         <v>1.18</v>
       </c>
       <c r="F32" s="5">
-        <v>23109.273528767997</v>
-      </c>
-      <c r="G32" s="62">
+        <v>15436.213255999999</v>
+      </c>
+      <c r="G32" s="69">
         <f>F32</f>
-        <v>23109.273528767997</v>
+        <v>15436.213255999999</v>
       </c>
       <c r="H32" s="8">
         <f t="shared" si="0"/>
@@ -2345,7 +2335,7 @@
       </c>
       <c r="L32" s="5">
         <f>C7*E32/100+1</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
       <c r="M32" s="5">
         <f>C8*E32/100</f>
@@ -2353,7 +2343,7 @@
       </c>
       <c r="N32" s="44">
         <f t="shared" si="8"/>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2371,11 +2361,11 @@
         <v>1.18</v>
       </c>
       <c r="F33" s="5">
-        <v>11067.659736</v>
-      </c>
-      <c r="G33" s="62">
+        <v>15436.213255999999</v>
+      </c>
+      <c r="G33" s="69">
         <f t="shared" si="9"/>
-        <v>11067.659736</v>
+        <v>15436.213255999999</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="0"/>
@@ -2394,7 +2384,7 @@
       </c>
       <c r="L33" s="5">
         <f>C7*E33/100+1</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
       <c r="M33" s="5">
         <f>C8*E33/100</f>
@@ -2402,7 +2392,7 @@
       </c>
       <c r="N33" s="44">
         <f>K33+L33+M33</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
       <c r="O33" s="59"/>
     </row>
@@ -2414,34 +2404,39 @@
         <v>41</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="55"/>
+        <v>79</v>
+      </c>
+      <c r="D34" s="55" t="s">
+        <v>82</v>
+      </c>
       <c r="E34" s="1">
         <v>1.18</v>
       </c>
       <c r="F34" s="5">
-        <v>11067.659736</v>
-      </c>
-      <c r="G34" s="62"/>
+        <v>27477.827048767998</v>
+      </c>
+      <c r="G34" s="69">
+        <f>F34</f>
+        <v>27477.827048767998</v>
+      </c>
       <c r="H34" s="8">
         <f t="shared" si="0"/>
-        <v>11067.659736</v>
+        <v>0</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>973.9540567680001</v>
+        <v>0</v>
       </c>
       <c r="K34" s="44">
         <f t="shared" si="7"/>
-        <v>12041.613792767999</v>
+        <v>0</v>
       </c>
       <c r="L34" s="5">
         <f>C7*E34/100+1</f>
-        <v>15436.213255999999</v>
+        <v>14700.283363999999</v>
       </c>
       <c r="M34" s="5">
         <f>C8*E34/100</f>
@@ -2449,15 +2444,15 @@
       </c>
       <c r="N34" s="44">
         <f t="shared" si="8"/>
-        <v>27477.827048767998</v>
+        <v>14700.283363999999</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A35" s="64" t="s">
+      <c r="A35" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="64"/>
-      <c r="C35" s="64"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
       <c r="D35" s="52"/>
       <c r="E35" s="45">
         <f>SUM(E11:E34)</f>
@@ -2465,15 +2460,15 @@
       </c>
       <c r="F35" s="46">
         <f>SUM(F11:F34)</f>
-        <v>1772315.3825935232</v>
+        <v>2331198.1458783578</v>
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>831828.22012076806</v>
+        <v>1027656.6683125072</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>940487.16247275518</v>
+        <v>1303541.4775658506</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2481,12 +2476,12 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>82762.87029760248</v>
+        <v>114711.65002579484</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
         <f>SUM(L11:L34)</f>
-        <v>1307948.1131080007</v>
+        <v>1245587.4098020003</v>
       </c>
       <c r="M35" s="51">
         <f>SUM(M11:M34)</f>
@@ -2494,7 +2489,7 @@
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>2331198.1458783578</v>
+        <v>2663840.5373936449</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3270,11 +3265,11 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A29" s="70" t="s">
+      <c r="A29" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
       <c r="D29" s="27">
         <f>SUM(D5:D28)</f>
         <v>99.990000000000066</v>

--- a/FLORES DE ESTRADA/Mayo/PRORRATEO MAYO Estrada.xlsx
+++ b/FLORES DE ESTRADA/Mayo/PRORRATEO MAYO Estrada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B006D3EE-9EC7-48B2-A003-A007BB84086E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79BCAA0-A142-48F8-8571-A7B0652F7C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -721,6 +721,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="15" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -742,8 +744,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1103,22 +1103,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="67"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="69"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
@@ -1151,13 +1151,13 @@
       <c r="I4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="63">
+      <c r="J4" s="65">
         <v>1153202676</v>
       </c>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
@@ -1188,7 +1188,7 @@
         <v>56</v>
       </c>
       <c r="C7" s="50">
-        <v>1245701.98</v>
+        <v>1302201.98</v>
       </c>
       <c r="D7" s="53"/>
       <c r="F7" s="7"/>
@@ -1202,7 +1202,9 @@
       <c r="B8" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="29"/>
+      <c r="C8" s="29">
+        <v>700000</v>
+      </c>
       <c r="D8" s="29"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -1285,7 +1287,7 @@
       <c r="F11" s="5">
         <v>64095.377079999998</v>
       </c>
-      <c r="G11" s="69">
+      <c r="G11" s="62">
         <f>F11</f>
         <v>64095.377079999998</v>
       </c>
@@ -1304,15 +1306,15 @@
       </c>
       <c r="L11" s="5">
         <f>C7*E11/100</f>
-        <v>61039.397020000004</v>
+        <v>63807.897020000004</v>
       </c>
       <c r="M11" s="5">
         <f>C8*E11/100</f>
-        <v>0</v>
+        <v>34300.000000000007</v>
       </c>
       <c r="N11" s="44">
         <f>K11+L11+M11</f>
-        <v>61039.397020000004</v>
+        <v>98107.897020000004</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1334,7 +1336,7 @@
       <c r="F12" s="5">
         <v>423370.11607702024</v>
       </c>
-      <c r="G12" s="69"/>
+      <c r="G12" s="62"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
         <v>423370.11607702024</v>
@@ -1352,15 +1354,15 @@
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
-        <v>48457.807022000001</v>
+        <v>50655.657021999999</v>
       </c>
       <c r="M12" s="5">
         <f>C8*E12/100</f>
-        <v>0</v>
+        <v>27230</v>
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>509084.49331379804</v>
+        <v>538512.34331379808</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1382,7 +1384,7 @@
       <c r="F13" s="5">
         <v>58437.839409563472</v>
       </c>
-      <c r="G13" s="69">
+      <c r="G13" s="62">
         <f>F13</f>
         <v>58437.839409563472</v>
       </c>
@@ -1403,15 +1405,15 @@
       </c>
       <c r="L13" s="5">
         <f>C7*E13/100</f>
-        <v>49828.0792</v>
+        <v>52088.0792</v>
       </c>
       <c r="M13" s="5">
         <f>C8*E13/100</f>
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="N13" s="44">
         <f>K13+L13+M13</f>
-        <v>49828.0792</v>
+        <v>80088.079200000007</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1433,7 +1435,7 @@
       <c r="F14" s="5">
         <v>64095.377079999998</v>
       </c>
-      <c r="G14" s="69">
+      <c r="G14" s="62">
         <f t="shared" ref="G14" si="2">F14</f>
         <v>64095.377079999998</v>
       </c>
@@ -1454,15 +1456,15 @@
       </c>
       <c r="L14" s="5">
         <f>C7*E14/100</f>
-        <v>61039.397020000004</v>
+        <v>63807.897020000004</v>
       </c>
       <c r="M14" s="5">
         <f>C8*E14/100</f>
-        <v>0</v>
+        <v>34300.000000000007</v>
       </c>
       <c r="N14" s="44">
         <f t="shared" ref="N14:N24" si="3">K14+L14+M14</f>
-        <v>61039.397020000004</v>
+        <v>98107.897020000004</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1484,7 +1486,7 @@
       <c r="F15" s="5">
         <v>50883.880987999997</v>
       </c>
-      <c r="G15" s="69">
+      <c r="G15" s="62">
         <f t="shared" ref="G15:G21" si="4">F15</f>
         <v>50883.880987999997</v>
       </c>
@@ -1505,15 +1507,15 @@
       </c>
       <c r="L15" s="5">
         <f>C7*E15/100</f>
-        <v>48457.807022000001</v>
+        <v>50655.657021999999</v>
       </c>
       <c r="M15" s="5">
         <f>C8*E15/100</f>
-        <v>0</v>
+        <v>27230</v>
       </c>
       <c r="N15" s="44">
         <f>K15+L15+M15</f>
-        <v>48457.807022000001</v>
+        <v>77885.657021999999</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -1535,7 +1537,7 @@
       <c r="F16" s="5">
         <v>52322.756799999996</v>
       </c>
-      <c r="G16" s="69"/>
+      <c r="G16" s="62"/>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
         <v>52322.756799999996</v>
@@ -1553,15 +1555,15 @@
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
-        <v>49828.0792</v>
+        <v>52088.0792</v>
       </c>
       <c r="M16" s="5">
         <f>C8*E16/100</f>
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="N16" s="44">
         <f t="shared" si="3"/>
-        <v>106755.2385984</v>
+        <v>137015.2385984</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1583,7 +1585,7 @@
       <c r="F17" s="5">
         <v>64095.377079999998</v>
       </c>
-      <c r="G17" s="69">
+      <c r="G17" s="62">
         <f t="shared" si="4"/>
         <v>64095.377079999998</v>
       </c>
@@ -1604,15 +1606,15 @@
       </c>
       <c r="L17" s="5">
         <f>C7*E17/100</f>
-        <v>61039.397020000004</v>
+        <v>63807.897020000004</v>
       </c>
       <c r="M17" s="5">
         <f>C8*E17/100</f>
-        <v>0</v>
+        <v>34300.000000000007</v>
       </c>
       <c r="N17" s="44">
         <f>K17+L17+M17</f>
-        <v>61039.397020000004</v>
+        <v>98107.897020000004</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -1632,7 +1634,7 @@
       <c r="F18" s="5">
         <v>50883.880987999997</v>
       </c>
-      <c r="G18" s="69">
+      <c r="G18" s="62">
         <f t="shared" si="4"/>
         <v>50883.880987999997</v>
       </c>
@@ -1653,15 +1655,15 @@
       </c>
       <c r="L18" s="5">
         <f>C7*E18/100</f>
-        <v>48457.807022000001</v>
+        <v>50655.657021999999</v>
       </c>
       <c r="M18" s="5">
         <f>C8*E18/100</f>
-        <v>0</v>
+        <v>27230</v>
       </c>
       <c r="N18" s="44">
         <f t="shared" si="3"/>
-        <v>48457.807022000001</v>
+        <v>77885.657021999999</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -1683,7 +1685,7 @@
       <c r="F19" s="5">
         <v>52322.756799999996</v>
       </c>
-      <c r="G19" s="69">
+      <c r="G19" s="62">
         <f>F19</f>
         <v>52322.756799999996</v>
       </c>
@@ -1704,15 +1706,15 @@
       </c>
       <c r="L19" s="5">
         <f>C7*E19/100</f>
-        <v>49828.0792</v>
+        <v>52088.0792</v>
       </c>
       <c r="M19" s="5">
         <f>C8*E19/100</f>
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="N19" s="44">
         <f t="shared" si="3"/>
-        <v>49828.0792</v>
+        <v>80088.079200000007</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -1732,36 +1734,36 @@
       <c r="F20" s="5">
         <v>165601.525272</v>
       </c>
-      <c r="G20" s="69">
-        <f t="shared" si="4"/>
-        <v>165601.525272</v>
+      <c r="G20" s="62">
+        <f>F20+237000</f>
+        <v>402601.525272</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-237000</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
       </c>
       <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-20856.000000000004</v>
       </c>
       <c r="K20" s="44">
         <f>H20+J20+I20</f>
-        <v>0</v>
+        <v>-257856</v>
       </c>
       <c r="L20" s="5">
         <f>C7*E20/100</f>
-        <v>157705.87066799999</v>
+        <v>164858.77066800001</v>
       </c>
       <c r="M20" s="5">
         <f>C8*E20/100</f>
-        <v>0</v>
+        <v>88620</v>
       </c>
       <c r="N20" s="44">
         <f>K20+L20+M20</f>
-        <v>157705.87066799999</v>
+        <v>-4377.2293319999881</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -1783,7 +1785,7 @@
       <c r="F21" s="5">
         <v>101375.34129999999</v>
       </c>
-      <c r="G21" s="70">
+      <c r="G21" s="63">
         <f t="shared" si="4"/>
         <v>101375.34129999999</v>
       </c>
@@ -1804,15 +1806,15 @@
       </c>
       <c r="L21" s="5">
         <f>C7*E21/100</f>
-        <v>96541.903450000013</v>
+        <v>100920.65345000001</v>
       </c>
       <c r="M21" s="5">
         <f>C8*E21/100</f>
-        <v>0</v>
+        <v>54250</v>
       </c>
       <c r="N21" s="44">
         <f t="shared" si="3"/>
-        <v>96541.903450000013</v>
+        <v>155170.65345000001</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -1834,7 +1836,7 @@
       <c r="F22" s="5">
         <v>174866.77987817599</v>
       </c>
-      <c r="G22" s="69">
+      <c r="G22" s="62">
         <f>F22</f>
         <v>174866.77987817599</v>
       </c>
@@ -1855,15 +1857,15 @@
       </c>
       <c r="L22" s="5">
         <f>C7*E22/100</f>
-        <v>93552.218697999997</v>
+        <v>97795.368697999991</v>
       </c>
       <c r="M22" s="5">
         <f>C8*E22/100</f>
-        <v>0</v>
+        <v>52570</v>
       </c>
       <c r="N22" s="44">
         <f t="shared" si="3"/>
-        <v>93552.218697999997</v>
+        <v>150365.36869799998</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1883,7 +1885,7 @@
       <c r="F23" s="5">
         <v>103616.13454832</v>
       </c>
-      <c r="G23" s="69"/>
+      <c r="G23" s="62"/>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
         <v>103616.13454832</v>
@@ -1901,15 +1903,15 @@
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
-        <v>55433.738109999998</v>
+        <v>57947.988109999998</v>
       </c>
       <c r="M23" s="5">
         <f>C8*E23/100</f>
-        <v>0</v>
+        <v>31150</v>
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>168168.09249857216</v>
+        <v>201832.34249857216</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1929,7 +1931,7 @@
       <c r="F24" s="5">
         <v>80707.852363999991</v>
       </c>
-      <c r="G24" s="69">
+      <c r="G24" s="62">
         <f>F24</f>
         <v>80707.852363999991</v>
       </c>
@@ -1950,15 +1952,15 @@
       </c>
       <c r="L24" s="5">
         <f>C7*E24/100</f>
-        <v>76859.812166000003</v>
+        <v>80345.862166000006</v>
       </c>
       <c r="M24" s="5">
         <f>C8*E24/100</f>
-        <v>0</v>
+        <v>43190</v>
       </c>
       <c r="N24" s="44">
         <f t="shared" si="3"/>
-        <v>76859.812166000003</v>
+        <v>123535.86216600001</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -1980,7 +1982,7 @@
       <c r="F25" s="5">
         <v>155397.25435222301</v>
       </c>
-      <c r="G25" s="69"/>
+      <c r="G25" s="62"/>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
         <v>155397.25435222301</v>
@@ -1998,15 +2000,15 @@
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
-        <v>55434.738109999998</v>
+        <v>57948.988109999998</v>
       </c>
       <c r="M25" s="5">
         <f>C8*E25/100</f>
-        <v>0</v>
+        <v>31150</v>
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>224506.95084521864</v>
+        <v>258171.20084521864</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2028,7 +2030,7 @@
       <c r="F26" s="5">
         <v>486959.29469553451</v>
       </c>
-      <c r="G26" s="69"/>
+      <c r="G26" s="62"/>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
         <v>486959.29469553451</v>
@@ -2046,15 +2048,15 @@
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
-        <v>114481.011962</v>
+        <v>119673.36196199998</v>
       </c>
       <c r="M26" s="5">
         <f>C8*E26/100</f>
-        <v>0</v>
+        <v>64330</v>
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>644292.72459074156</v>
+        <v>713815.07459074154</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2076,7 +2078,7 @@
       <c r="F27" s="5">
         <v>15436.213255999999</v>
       </c>
-      <c r="G27" s="69">
+      <c r="G27" s="62">
         <f>F27</f>
         <v>15436.213255999999</v>
       </c>
@@ -2097,15 +2099,15 @@
       </c>
       <c r="L27" s="5">
         <f>C7*E27/100+1</f>
-        <v>14700.283363999999</v>
+        <v>15366.983364</v>
       </c>
       <c r="M27" s="5">
         <f>C8*E27/100</f>
-        <v>0</v>
+        <v>8260</v>
       </c>
       <c r="N27" s="44">
         <f>K27+L27+M27</f>
-        <v>14700.283363999999</v>
+        <v>23626.983364</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2125,7 +2127,7 @@
       <c r="F28" s="5">
         <v>15436.213255999999</v>
       </c>
-      <c r="G28" s="69"/>
+      <c r="G28" s="62"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
         <v>15436.213255999999</v>
@@ -2143,15 +2145,15 @@
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
-        <v>14700.283363999999</v>
+        <v>15366.983364</v>
       </c>
       <c r="M28" s="5">
         <f>C8*E28/100</f>
-        <v>0</v>
+        <v>8260</v>
       </c>
       <c r="N28" s="44">
         <f t="shared" ref="N28:N34" si="8">K28+L28+M28</f>
-        <v>31494.883386527999</v>
+        <v>40421.583386528</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2171,7 +2173,7 @@
       <c r="F29" s="5">
         <v>15436.213255999999</v>
       </c>
-      <c r="G29" s="69"/>
+      <c r="G29" s="62"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
         <v>15436.213255999999</v>
@@ -2189,15 +2191,15 @@
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
-        <v>14700.283363999999</v>
+        <v>15366.983364</v>
       </c>
       <c r="M29" s="5">
         <f>C8*E29/100</f>
-        <v>0</v>
+        <v>8260</v>
       </c>
       <c r="N29" s="44">
         <f t="shared" si="8"/>
-        <v>31494.883386527999</v>
+        <v>40421.583386528</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2217,7 +2219,7 @@
       <c r="F30" s="5">
         <v>62071.494580752566</v>
       </c>
-      <c r="G30" s="69">
+      <c r="G30" s="62">
         <v>11068</v>
       </c>
       <c r="H30" s="60">
@@ -2237,15 +2239,15 @@
       </c>
       <c r="L30" s="5">
         <f>C7*E30/100+1</f>
-        <v>14700.283363999999</v>
+        <v>15366.983364</v>
       </c>
       <c r="M30" s="5">
         <f>C8*E30/100</f>
-        <v>0</v>
+        <v>8260</v>
       </c>
       <c r="N30" s="44">
         <f>K30+L30+M30</f>
-        <v>70192.085467858793</v>
+        <v>79118.78546785879</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2265,8 +2267,8 @@
       <c r="F31" s="5">
         <v>15436.213255999999</v>
       </c>
-      <c r="G31" s="69">
-        <f t="shared" ref="G29:G33" si="9">F31</f>
+      <c r="G31" s="62">
+        <f t="shared" ref="G31:G33" si="9">F31</f>
         <v>15436.213255999999</v>
       </c>
       <c r="H31" s="8">
@@ -2286,15 +2288,15 @@
       </c>
       <c r="L31" s="5">
         <f>C7*E31/100+1</f>
-        <v>14700.283363999999</v>
+        <v>15366.983364</v>
       </c>
       <c r="M31" s="5">
         <f>C8*E31/100</f>
-        <v>0</v>
+        <v>8260</v>
       </c>
       <c r="N31" s="44">
         <f>K31+L31+M31</f>
-        <v>14700.283363999999</v>
+        <v>23626.983364</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -2314,7 +2316,7 @@
       <c r="F32" s="5">
         <v>15436.213255999999</v>
       </c>
-      <c r="G32" s="69">
+      <c r="G32" s="62">
         <f>F32</f>
         <v>15436.213255999999</v>
       </c>
@@ -2335,15 +2337,15 @@
       </c>
       <c r="L32" s="5">
         <f>C7*E32/100+1</f>
-        <v>14700.283363999999</v>
+        <v>15366.983364</v>
       </c>
       <c r="M32" s="5">
         <f>C8*E32/100</f>
-        <v>0</v>
+        <v>8260</v>
       </c>
       <c r="N32" s="44">
         <f t="shared" si="8"/>
-        <v>14700.283363999999</v>
+        <v>23626.983364</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2363,7 +2365,7 @@
       <c r="F33" s="5">
         <v>15436.213255999999</v>
       </c>
-      <c r="G33" s="69">
+      <c r="G33" s="62">
         <f t="shared" si="9"/>
         <v>15436.213255999999</v>
       </c>
@@ -2384,15 +2386,15 @@
       </c>
       <c r="L33" s="5">
         <f>C7*E33/100+1</f>
-        <v>14700.283363999999</v>
+        <v>15366.983364</v>
       </c>
       <c r="M33" s="5">
         <f>C8*E33/100</f>
-        <v>0</v>
+        <v>8260</v>
       </c>
       <c r="N33" s="44">
         <f>K33+L33+M33</f>
-        <v>14700.283363999999</v>
+        <v>23626.983364</v>
       </c>
       <c r="O33" s="59"/>
     </row>
@@ -2415,7 +2417,7 @@
       <c r="F34" s="5">
         <v>27477.827048767998</v>
       </c>
-      <c r="G34" s="69">
+      <c r="G34" s="62">
         <f>F34</f>
         <v>27477.827048767998</v>
       </c>
@@ -2436,23 +2438,23 @@
       </c>
       <c r="L34" s="5">
         <f>C7*E34/100+1</f>
-        <v>14700.283363999999</v>
+        <v>15366.983364</v>
       </c>
       <c r="M34" s="5">
         <f>C8*E34/100</f>
-        <v>0</v>
+        <v>8260</v>
       </c>
       <c r="N34" s="44">
         <f t="shared" si="8"/>
-        <v>14700.283363999999</v>
+        <v>23626.983364</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A35" s="62" t="s">
+      <c r="A35" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="62"/>
-      <c r="C35" s="62"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="64"/>
       <c r="D35" s="52"/>
       <c r="E35" s="45">
         <f>SUM(E11:E34)</f>
@@ -2464,11 +2466,11 @@
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>1027656.6683125072</v>
+        <v>1264656.6683125077</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>1303541.4775658506</v>
+        <v>1066541.4775658501</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2476,20 +2478,20 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>114711.65002579484</v>
+        <v>93855.650025794836</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
         <f>SUM(L11:L34)</f>
-        <v>1245587.4098020003</v>
+        <v>1302081.7598019997</v>
       </c>
       <c r="M35" s="51">
         <f>SUM(M11:M34)</f>
-        <v>0</v>
+        <v>699930</v>
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>2663840.5373936449</v>
+        <v>3162408.8873936455</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3265,11 +3267,11 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A29" s="68" t="s">
+      <c r="A29" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
       <c r="D29" s="27">
         <f>SUM(D5:D28)</f>
         <v>99.990000000000066</v>
